--- a/questionnaire_templates/004_workforce_capability_index_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/004_workforce_capability_index_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -719,8 +719,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'accounting_and_finance',_'label':_'accounting_and_finance'}</t>
+          <t>accounting_and_finance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Accounting and Finance', 'label': 'Accounting and Finance'}</t>
+          <t>Accounting and Finance</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'engineering',_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Engineering', 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'it',_'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'IT', 'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'management',_'label':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Management', 'label': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'research',_'label':_'research'}</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Research', 'label': 'Research'}</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'analytical',_'label':_'analytical'}</t>
+          <t>analytical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Analytical', 'label': 'Analytical'}</t>
+          <t>Analytical</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'communication',_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Communication', 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'leadership',_'label':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Leadership', 'label': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'problem_solving',_'label':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Problem Solving', 'label': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'technical',_'label':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Technical', 'label': 'Technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'time_management',_'label':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Time Management', 'label': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'workforce_development',_'label':_'workforce_development'}</t>
+          <t>workforce_development</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Workforce Development', 'label': 'Workforce Development'}</t>
+          <t>Workforce Development</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_0,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 0, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
